--- a/public/downloads/MarginCOS_Data_Template_v3.2_Manufacturing.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Manufacturing.xlsx
@@ -757,7 +757,6 @@
     <comment ref="J4" authorId="0" shapeId="0">
       <text>
         <t>Price Elasticity
-──────────────────────────────
 Sensitivity of volume to a 1% price change.
 Format: Negative decimal between -3.0 and 0.0
 More negative = more price-sensitive
@@ -1086,7 +1085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="B2:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="59" min="1" max="1"/>
@@ -1128,8 +1127,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
     <row r="7" ht="18" customHeight="1" s="59">
       <c r="B7" s="3" t="inlineStr">
         <is>
@@ -1185,7 +1182,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="18" customHeight="1" s="59">
       <c r="B13" s="9" t="inlineStr">
         <is>
@@ -1278,7 +1274,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="15" customHeight="1" s="59">
       <c r="B22" s="62" t="inlineStr">
         <is>

--- a/public/downloads/MarginCOS_Data_Template_v3.2_Manufacturing.xlsx
+++ b/public/downloads/MarginCOS_Data_Template_v3.2_Manufacturing.xlsx
@@ -32016,7 +32016,7 @@
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="K1:N1"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="E5:E1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="Invalid Segment" error="Choose: Mass Market, Mid-Range, or Premium." promptTitle="Segment" prompt="Select the price segment for this SKU." type="list">
       <formula1>"Mass Market,Mid-Range,Premium"</formula1>
       <formula2>0</formula2>
@@ -32060,6 +32060,9 @@
     <dataValidation sqref="B5:B1004" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Duplicate SKU ID" error="This SKU ID already exists in your upload. Each row must have a unique SKU ID." type="custom">
       <formula1>COUNTIF($B$5:$B$1004,B5)=1</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation sqref="D5:D1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Category" error="Please select from the dropdown list." promptTitle="Category" prompt="Select the product category from the Reference_Lists sheet." type="list" errorStyle="warning">
+      <formula1>=Reference_Lists!$B$4:$B$46</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
